--- a/public/gold-answer-library-template.xlsx
+++ b/public/gold-answer-library-template.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>A. Broyles</t>
+          <t>[your name]</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>AWS KMS</t>
+          <t>[cloud provider] KMS</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>EXAMPLE - Current subprocessors: AWS (hosting, all customer data), Stripe (billing, payment metadata only), Anthropic (AI processing, document text). Full list maintained at [your trust page URL].</t>
+          <t>EXAMPLE - Current subprocessors: [cloud provider] (hosting, all customer data), [payment processor] (billing, payment metadata only), [AI provider] (AI processing, document text). Full list maintained at [your trust page URL].</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>A. Broyles</t>
+          <t>[your name]</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>AWS; Stripe; Anthropic</t>
+          <t>[cloud provider]; [payment processor]; [AI provider]</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>EXAMPLE - AWS</t>
+          <t>EXAMPLE - [cloud provider]</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
